--- a/部分名词对照.xlsx
+++ b/部分名词对照.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\53062\Documents\GitHub\Omega-no-shikai_CN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BB6D3C-83CD-41DD-B7B0-4A784E7C5807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE757DD-3654-432D-9F5C-5BE1641F8226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="870" windowWidth="19200" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6050" yWindow="6420" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -2719,10 +2719,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>卡莉娅</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>クララ</t>
     </r>
@@ -3371,6 +3367,10 @@
       </rPr>
       <t>リデル</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡利亚</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4367,7 +4367,7 @@
         <v>98</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>94</v>
@@ -4391,7 +4391,7 @@
         <v>102</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>428</v>
+        <v>518</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>351</v>
@@ -4460,10 +4460,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>94</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>86</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>86</v>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>44</v>
@@ -4640,10 +4640,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>6</v>
@@ -4712,10 +4712,10 @@
     </row>
     <row r="76" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>6</v>
@@ -4763,7 +4763,7 @@
         <v>148</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>149</v>
@@ -4775,7 +4775,7 @@
         <v>369</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>44</v>
@@ -4787,7 +4787,7 @@
         <v>150</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>44</v>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>6</v>
@@ -4832,10 +4832,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>6</v>
@@ -4928,7 +4928,7 @@
     </row>
     <row r="94" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>317</v>
@@ -4952,13 +4952,13 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="C96" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -5051,7 +5051,7 @@
         <v>190</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>191</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>6</v>
@@ -5096,10 +5096,10 @@
     </row>
     <row r="108" spans="1:4" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>197</v>
@@ -5123,7 +5123,7 @@
         <v>199</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>200</v>
@@ -5132,10 +5132,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>6</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>200</v>
@@ -5219,7 +5219,7 @@
         <v>210</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>44</v>
@@ -5231,7 +5231,7 @@
         <v>211</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>44</v>
@@ -5243,7 +5243,7 @@
         <v>212</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>44</v>
@@ -5267,7 +5267,7 @@
         <v>215</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>44</v>
@@ -5375,7 +5375,7 @@
         <v>320</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>6</v>
@@ -5447,7 +5447,7 @@
         <v>245</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>246</v>
@@ -5492,7 +5492,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>253</v>
@@ -5564,10 +5564,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>265</v>
@@ -5591,7 +5591,7 @@
         <v>268</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>269</v>
@@ -5603,7 +5603,7 @@
         <v>394</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>44</v>
@@ -5627,7 +5627,7 @@
         <v>274</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>323</v>
@@ -5663,7 +5663,7 @@
         <v>280</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>281</v>
@@ -5843,7 +5843,7 @@
         <v>305</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>6</v>
@@ -5876,13 +5876,13 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="D173" s="2"/>
     </row>
@@ -5903,10 +5903,10 @@
         <v>357</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="D175" s="2"/>
     </row>
@@ -5933,34 +5933,34 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="C178" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D178" s="2"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>470</v>
-      </c>
       <c r="C179" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D179" s="2"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="C180" t="s">
         <v>6</v>
@@ -5981,10 +5981,10 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="C182" t="s">
         <v>86</v>
@@ -5993,10 +5993,10 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C183" t="s">
         <v>86</v>
@@ -6005,10 +6005,10 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B184" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="C184" t="s">
         <v>6</v>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B185" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="C185" t="s">
         <v>6</v>
@@ -6074,7 +6074,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>161</v>
@@ -6086,7 +6086,7 @@
         <v>374</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C191" t="s">
         <v>6</v>
@@ -6127,15 +6127,15 @@
         <v>381</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="C196" t="s">
         <v>6</v>
@@ -6143,10 +6143,10 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="C197" t="s">
         <v>6</v>
@@ -6157,7 +6157,7 @@
         <v>382</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C198" t="s">
         <v>6</v>
@@ -6176,15 +6176,15 @@
         <v>385</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C201" t="s">
         <v>6</v>
@@ -6195,7 +6195,7 @@
         <v>386</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -6244,7 +6244,7 @@
         <v>395</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C207" t="s">
         <v>6</v>
@@ -6255,7 +6255,7 @@
         <v>396</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C208" t="s">
         <v>6</v>
@@ -6277,7 +6277,7 @@
         <v>399</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>6</v>
@@ -6288,7 +6288,7 @@
         <v>400</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>6</v>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="214" spans="1:3" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A214" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>6</v>
@@ -6354,7 +6354,7 @@
         <v>410</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -6362,7 +6362,7 @@
         <v>411</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -6394,10 +6394,10 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="C222" t="s">
         <v>6</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B223" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="C223" t="s">
         <v>409</v>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C224" t="s">
         <v>6</v>
@@ -6427,10 +6427,10 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C225" t="s">
         <v>6</v>
@@ -6438,10 +6438,10 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="C226" t="s">
         <v>6</v>
@@ -6449,10 +6449,10 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="C227" t="s">
         <v>6</v>
